--- a/C/chrXVI:399186-498981_63_finemapping.xlsx
+++ b/C/chrXVI:399186-498981_63_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3433" uniqueCount="3433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3425" uniqueCount="3425">
   <si>
     <t xml:space="preserve">seqnames</t>
   </si>
@@ -9155,19 +9155,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -9663,21 +9654,6 @@
   </si>
   <si>
     <t xml:space="preserve">RPL43B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -10916,48 +10892,42 @@
         <v>3043</v>
       </c>
       <c r="Z1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3044</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3045</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3046</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3047</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3048</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3049</v>
       </c>
-      <c r="AF1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3050</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3051</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3052</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3053</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>3055</v>
+        <v>3052</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -11011,59 +10981,57 @@
         <v>415343</v>
       </c>
       <c r="U2" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="V2" t="n">
         <v>326270</v>
       </c>
       <c r="W2" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.152913894364704</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0295980392411793</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3056</v>
       </c>
       <c r="AD2" t="s">
         <v>35</v>
       </c>
       <c r="AE2" t="s">
-        <v>3059</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3059</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>3056</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="b">
+      <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>3060</v>
+      <c r="AH2" t="s">
+        <v>3057</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>3061</v>
+        <v>3058</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
@@ -11117,62 +11085,60 @@
         <v>460761</v>
       </c>
       <c r="U3" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
       <c r="V3" t="n">
         <v>453565</v>
       </c>
       <c r="W3" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.242836866100477</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0471487507162986</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3062</v>
       </c>
       <c r="AD3" t="s">
         <v>35</v>
       </c>
       <c r="AE3" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>3062</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="b">
+      <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>3066</v>
+      <c r="AH3" t="s">
+        <v>3063</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>3067</v>
+        <v>3064</v>
       </c>
       <c r="D4" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="E4" t="n">
         <v>428479</v>
@@ -11223,59 +11189,57 @@
         <v>428479</v>
       </c>
       <c r="U4" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V4" t="n">
         <v>35383</v>
       </c>
       <c r="W4" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.919195709064195</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.178538157782115</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3067</v>
       </c>
       <c r="AD4" t="s">
         <v>35</v>
       </c>
       <c r="AE4" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" t="b">
+      <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>3067</v>
+      <c r="AH4" t="s">
+        <v>3064</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>3071</v>
+        <v>3068</v>
       </c>
       <c r="D5" t="s">
         <v>106</v>
@@ -11329,62 +11293,60 @@
         <v>444980</v>
       </c>
       <c r="U5" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V5" t="n">
         <v>368781</v>
       </c>
       <c r="W5" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.292197072396712</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0595633630693351</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3067</v>
       </c>
       <c r="AD5" t="s">
         <v>35</v>
       </c>
       <c r="AE5" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="b">
+      <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>3072</v>
+      <c r="AH5" t="s">
+        <v>3069</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>3073</v>
+        <v>3070</v>
       </c>
       <c r="D6" t="s">
-        <v>3074</v>
+        <v>3071</v>
       </c>
       <c r="E6" t="n">
         <v>382894</v>
@@ -11435,59 +11397,57 @@
         <v>405846</v>
       </c>
       <c r="U6" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="V6" t="n">
         <v>6401</v>
       </c>
       <c r="W6" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.89761105282275</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.40721751217291</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3073</v>
       </c>
       <c r="AD6" t="s">
         <v>35</v>
       </c>
       <c r="AE6" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AH6" t="n">
+        <v>3073</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" t="b">
+      <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>3077</v>
+      <c r="AH6" t="s">
+        <v>3074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>3078</v>
+        <v>3075</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -11541,59 +11501,57 @@
         <v>460761</v>
       </c>
       <c r="U7" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="V7" t="n">
         <v>159473</v>
       </c>
       <c r="W7" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.190633022235304</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0460426887274137</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3077</v>
       </c>
       <c r="AD7" t="s">
         <v>35</v>
       </c>
       <c r="AE7" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>3081</v>
+        <v>3077</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>3078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>3082</v>
+        <v>3079</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -11647,59 +11605,57 @@
         <v>460761</v>
       </c>
       <c r="U8" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="V8" t="n">
         <v>555650</v>
       </c>
       <c r="W8" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.150335398322579</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0382045702033131</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3081</v>
       </c>
       <c r="AD8" t="s">
         <v>35</v>
       </c>
       <c r="AE8" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AH8" t="n">
+        <v>3081</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" t="b">
+      <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>3085</v>
+      <c r="AH8" t="s">
+        <v>3082</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>3086</v>
+        <v>3083</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -11753,59 +11709,57 @@
         <v>460761</v>
       </c>
       <c r="U9" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="V9" t="n">
         <v>220138</v>
       </c>
       <c r="W9" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.292365029955164</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0786873596807103</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3085</v>
       </c>
       <c r="AD9" t="s">
         <v>35</v>
       </c>
       <c r="AE9" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AH9" t="n">
+        <v>3085</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" t="b">
+      <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>3089</v>
+      <c r="AH9" t="s">
+        <v>3086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>3090</v>
+        <v>3087</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -11859,59 +11813,57 @@
         <v>460761</v>
       </c>
       <c r="U10" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="V10" t="n">
         <v>142174</v>
       </c>
       <c r="W10" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-0.172874341346082</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0479114536751562</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3089</v>
       </c>
       <c r="AD10" t="s">
         <v>35</v>
       </c>
       <c r="AE10" t="s">
-        <v>3092</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3092</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>3089</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" t="b">
+      <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>3093</v>
+      <c r="AH10" t="s">
+        <v>3090</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>3094</v>
+        <v>3091</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -11965,62 +11917,60 @@
         <v>460761</v>
       </c>
       <c r="U11" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="V11" t="n">
         <v>85676</v>
       </c>
       <c r="W11" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.225527481814097</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0605791820594207</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3093</v>
       </c>
       <c r="AD11" t="s">
         <v>35</v>
       </c>
       <c r="AE11" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>3093</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" t="b">
+      <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>3097</v>
+      <c r="AH11" t="s">
+        <v>3094</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>3098</v>
+        <v>3095</v>
       </c>
       <c r="D12" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="E12" t="n">
         <v>415343</v>
@@ -12071,59 +12021,57 @@
         <v>428479</v>
       </c>
       <c r="U12" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="V12" t="n">
         <v>254418</v>
       </c>
       <c r="W12" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-0.211171401422214</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0564257274942718</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3097</v>
       </c>
       <c r="AD12" t="s">
         <v>35</v>
       </c>
       <c r="AE12" t="s">
-        <v>3100</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3100</v>
-      </c>
-      <c r="AH12" t="n">
+        <v>3097</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" t="b">
+      <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>3098</v>
+      <c r="AH12" t="s">
+        <v>3095</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>3101</v>
+        <v>3098</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
@@ -12177,59 +12125,57 @@
         <v>460761</v>
       </c>
       <c r="U13" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="V13" t="n">
         <v>678083</v>
       </c>
       <c r="W13" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.149907157082166</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0414297815742939</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3077</v>
       </c>
       <c r="AD13" t="s">
         <v>35</v>
       </c>
       <c r="AE13" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>3077</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" t="b">
+      <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>3102</v>
+      <c r="AH13" t="s">
+        <v>3099</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -12283,59 +12229,57 @@
         <v>451866</v>
       </c>
       <c r="U14" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="V14" t="n">
         <v>122299</v>
       </c>
       <c r="W14" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.216837693053018</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0601546402521914</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3093</v>
       </c>
       <c r="AD14" t="s">
         <v>35</v>
       </c>
       <c r="AE14" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AH14" t="n">
+        <v>3093</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" t="b">
+      <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>3104</v>
+      <c r="AH14" t="s">
+        <v>3101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>3105</v>
+        <v>3102</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -12389,59 +12333,57 @@
         <v>451866</v>
       </c>
       <c r="U15" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
       <c r="V15" t="n">
         <v>162479</v>
       </c>
       <c r="W15" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-0.21485703250715</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0588039753700857</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3104</v>
       </c>
       <c r="AD15" t="s">
         <v>35</v>
       </c>
       <c r="AE15" t="s">
-        <v>3107</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3107</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>3104</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="b">
+      <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>3105</v>
+      <c r="AH15" t="s">
+        <v>3102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>3108</v>
+        <v>3105</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
@@ -12495,59 +12437,57 @@
         <v>415343</v>
       </c>
       <c r="U16" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="V16" t="n">
         <v>451327</v>
       </c>
       <c r="W16" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.123574567779772</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0341079457181899</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3073</v>
       </c>
       <c r="AD16" t="s">
         <v>35</v>
       </c>
       <c r="AE16" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AH16" t="n">
+        <v>3073</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" t="b">
+      <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>3109</v>
+      <c r="AH16" t="s">
+        <v>3106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>3110</v>
+        <v>3107</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
@@ -12601,59 +12541,57 @@
         <v>460761</v>
       </c>
       <c r="U17" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V17" t="n">
         <v>805887</v>
       </c>
       <c r="W17" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.187187054069913</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.0568113204706419</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3067</v>
       </c>
       <c r="AD17" t="s">
         <v>35</v>
       </c>
       <c r="AE17" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" t="b">
+      <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>3111</v>
+      <c r="AH17" t="s">
+        <v>3108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>3112</v>
+        <v>3109</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>
@@ -12707,59 +12645,57 @@
         <v>415343</v>
       </c>
       <c r="U18" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="V18" t="n">
         <v>470960</v>
       </c>
       <c r="W18" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.218015164505068</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0722375393224914</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3073</v>
       </c>
       <c r="AD18" t="s">
         <v>35</v>
       </c>
       <c r="AE18" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>3073</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" t="b">
+      <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>3113</v>
+      <c r="AH18" t="s">
+        <v>3110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>3114</v>
+        <v>3111</v>
       </c>
       <c r="D19" t="s">
         <v>29</v>
@@ -12813,59 +12749,57 @@
         <v>460761</v>
       </c>
       <c r="U19" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="V19" t="n">
         <v>381869</v>
       </c>
       <c r="W19" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.0963857895340072</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0313240351024201</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>3073</v>
       </c>
       <c r="AD19" t="s">
         <v>35</v>
       </c>
       <c r="AE19" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>3073</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="b">
+      <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>3115</v>
+      <c r="AH19" t="s">
+        <v>3112</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>3116</v>
+        <v>3113</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
@@ -12919,59 +12853,57 @@
         <v>460761</v>
       </c>
       <c r="U20" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V20" t="n">
         <v>780709</v>
       </c>
       <c r="W20" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.0925210681152329</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0297376287654989</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3067</v>
       </c>
       <c r="AD20" t="s">
         <v>35</v>
       </c>
       <c r="AE20" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>3117</v>
+      <c r="AH20" t="s">
+        <v>3114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -13025,59 +12957,57 @@
         <v>451866</v>
       </c>
       <c r="U21" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
       <c r="V21" t="n">
         <v>162825</v>
       </c>
       <c r="W21" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.544773599639585</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.195650827467048</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3104</v>
       </c>
       <c r="AD21" t="s">
         <v>35</v>
       </c>
       <c r="AE21" t="s">
-        <v>3107</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3107</v>
-      </c>
-      <c r="AH21" t="n">
+        <v>3104</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" t="b">
+      <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>3119</v>
+      <c r="AH21" t="s">
+        <v>3116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>3120</v>
+        <v>3117</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
@@ -13131,59 +13061,57 @@
         <v>460761</v>
       </c>
       <c r="U22" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
       <c r="V22" t="n">
         <v>177365</v>
       </c>
       <c r="W22" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z22" t="n">
         <v>-0.199945999673898</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0646058367945629</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3104</v>
       </c>
       <c r="AD22" t="s">
         <v>35</v>
       </c>
       <c r="AE22" t="s">
-        <v>3107</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3107</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>3104</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" t="b">
+      <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>3121</v>
+      <c r="AH22" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>3122</v>
+        <v>3119</v>
       </c>
       <c r="D23" t="s">
         <v>106</v>
@@ -13237,59 +13165,57 @@
         <v>444980</v>
       </c>
       <c r="U23" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="V23" t="n">
         <v>504350</v>
       </c>
       <c r="W23" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.198010385977373</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0649364186504637</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3073</v>
       </c>
       <c r="AD23" t="s">
         <v>35</v>
       </c>
       <c r="AE23" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>3073</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>3123</v>
+      <c r="AH23" t="s">
+        <v>3120</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>3124</v>
+        <v>3121</v>
       </c>
       <c r="D24" t="s">
         <v>29</v>
@@ -13343,59 +13269,57 @@
         <v>460761</v>
       </c>
       <c r="U24" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
       <c r="V24" t="n">
         <v>604508</v>
       </c>
       <c r="W24" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-0.140864838244103</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.0518108222548736</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>3123</v>
       </c>
       <c r="AD24" t="s">
         <v>35</v>
       </c>
       <c r="AE24" t="s">
-        <v>3126</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>3126</v>
-      </c>
-      <c r="AH24" t="n">
+        <v>3123</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" t="b">
+      <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="s">
-        <v>3127</v>
+      <c r="AH24" t="s">
+        <v>3124</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>3128</v>
+        <v>3125</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
@@ -13449,59 +13373,57 @@
         <v>460761</v>
       </c>
       <c r="U25" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V25" t="n">
         <v>47805</v>
       </c>
       <c r="W25" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-0.236300284272826</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0800421989344128</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>3067</v>
       </c>
       <c r="AD25" t="s">
         <v>35</v>
       </c>
       <c r="AE25" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH25" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" t="b">
+      <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="s">
-        <v>3129</v>
+      <c r="AH25" t="s">
+        <v>3126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>3130</v>
+        <v>3127</v>
       </c>
       <c r="D26" t="s">
         <v>106</v>
@@ -13555,59 +13477,57 @@
         <v>444980</v>
       </c>
       <c r="U26" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
       <c r="V26" t="n">
         <v>300166</v>
       </c>
       <c r="W26" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.137306552165671</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0462261904318559</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>3123</v>
       </c>
       <c r="AD26" t="s">
         <v>35</v>
       </c>
       <c r="AE26" t="s">
-        <v>3126</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>3126</v>
-      </c>
-      <c r="AH26" t="n">
+        <v>3123</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" t="b">
+      <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="s">
-        <v>3131</v>
+      <c r="AH26" t="s">
+        <v>3128</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>3132</v>
+        <v>3129</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -13661,59 +13581,57 @@
         <v>460761</v>
       </c>
       <c r="U27" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="V27" t="n">
         <v>550109</v>
       </c>
       <c r="W27" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-0.155933915761495</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.0546167915821259</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>3085</v>
       </c>
       <c r="AD27" t="s">
         <v>35</v>
       </c>
       <c r="AE27" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AH27" t="n">
+        <v>3085</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="b">
+      <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>3133</v>
+      <c r="AH27" t="s">
+        <v>3130</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B28" t="s">
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
       <c r="D28" t="s">
         <v>106</v>
@@ -13767,59 +13685,57 @@
         <v>444980</v>
       </c>
       <c r="U28" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="V28" t="n">
         <v>253009</v>
       </c>
       <c r="W28" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z28" t="n">
         <v>-0.175362218222564</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.0573782860918258</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>3077</v>
       </c>
       <c r="AD28" t="s">
         <v>35</v>
       </c>
       <c r="AE28" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AH28" t="n">
+        <v>3077</v>
+      </c>
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" t="b">
+      <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="s">
-        <v>3135</v>
+      <c r="AH28" t="s">
+        <v>3132</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B29" t="s">
         <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>3136</v>
+        <v>3133</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -13873,59 +13789,57 @@
         <v>460761</v>
       </c>
       <c r="U29" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="V29" t="n">
         <v>551657</v>
       </c>
       <c r="W29" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.0961922367394856</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.0340597449814865</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>3056</v>
       </c>
       <c r="AD29" t="s">
         <v>35</v>
       </c>
       <c r="AE29" t="s">
-        <v>3059</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>3059</v>
-      </c>
-      <c r="AH29" t="n">
+        <v>3056</v>
+      </c>
+      <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" t="b">
+      <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>3137</v>
+      <c r="AH29" t="s">
+        <v>3134</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B30" t="s">
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="D30" t="s">
         <v>29</v>
@@ -13979,62 +13893,60 @@
         <v>460761</v>
       </c>
       <c r="U30" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="V30" t="n">
         <v>511315</v>
       </c>
       <c r="W30" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z30" t="n">
         <v>-0.238614366722789</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.0853351737615837</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>3085</v>
       </c>
       <c r="AD30" t="s">
         <v>35</v>
       </c>
       <c r="AE30" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AH30" t="n">
+        <v>3085</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" t="b">
+      <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>3138</v>
+      <c r="AH30" t="s">
+        <v>3135</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>3139</v>
+        <v>3136</v>
       </c>
       <c r="D31" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="E31" t="n">
         <v>405846</v>
@@ -14085,59 +13997,57 @@
         <v>431368</v>
       </c>
       <c r="U31" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="V31" t="n">
         <v>309695</v>
       </c>
       <c r="W31" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.0775184622382104</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.0281463028486269</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>3081</v>
       </c>
       <c r="AD31" t="s">
         <v>35</v>
       </c>
       <c r="AE31" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AH31" t="n">
+        <v>3081</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" t="b">
+      <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>3141</v>
+      <c r="AH31" t="s">
+        <v>3138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -14191,59 +14101,57 @@
         <v>460761</v>
       </c>
       <c r="U32" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="V32" t="n">
         <v>396769</v>
       </c>
       <c r="W32" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="Y32" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.100688185672796</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AA32" t="n">
         <v>0.0375097982442357</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>3093</v>
       </c>
       <c r="AD32" t="s">
         <v>35</v>
       </c>
       <c r="AE32" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AH32" t="n">
+        <v>3093</v>
+      </c>
+      <c r="AF32" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" t="b">
+      <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="s">
-        <v>3143</v>
+      <c r="AH32" t="s">
+        <v>3140</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -14297,59 +14205,57 @@
         <v>460761</v>
       </c>
       <c r="U33" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V33" t="n">
         <v>898651</v>
       </c>
       <c r="W33" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.131313661784565</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
         <v>0.0492752467532468</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>3067</v>
       </c>
       <c r="AD33" t="s">
         <v>35</v>
       </c>
       <c r="AE33" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH33" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" t="b">
+      <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>3145</v>
+      <c r="AH33" t="s">
+        <v>3142</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="D34" t="s">
         <v>29</v>
@@ -14403,62 +14309,60 @@
         <v>460761</v>
       </c>
       <c r="U34" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V34" t="n">
         <v>720541</v>
       </c>
       <c r="W34" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
       </c>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="Y34" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z34" t="n">
         <v>-0.191989838112144</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AA34" t="n">
         <v>0.0704215933555894</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>3067</v>
       </c>
       <c r="AD34" t="s">
         <v>35</v>
       </c>
       <c r="AE34" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH34" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF34" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" t="b">
+      <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>3147</v>
+      <c r="AH34" t="s">
+        <v>3144</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>3148</v>
+        <v>3145</v>
       </c>
       <c r="D35" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="E35" t="n">
         <v>428479</v>
@@ -14509,59 +14413,57 @@
         <v>432288</v>
       </c>
       <c r="U35" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="V35" t="n">
         <v>85880</v>
       </c>
       <c r="W35" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
       </c>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="Y35" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z35" t="n">
         <v>-0.408378611485702</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AA35" t="n">
         <v>0.169072508410678</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>3085</v>
       </c>
       <c r="AD35" t="s">
         <v>35</v>
       </c>
       <c r="AE35" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AH35" t="n">
+        <v>3085</v>
+      </c>
+      <c r="AF35" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" t="b">
+      <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>3150</v>
+      <c r="AH35" t="s">
+        <v>3147</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B36" t="s">
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>3151</v>
+        <v>3148</v>
       </c>
       <c r="D36" t="s">
         <v>29</v>
@@ -14615,59 +14517,57 @@
         <v>460761</v>
       </c>
       <c r="U36" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="V36" t="n">
         <v>331322</v>
       </c>
       <c r="W36" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
       </c>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="Y36" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.089701653852409</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AA36" t="n">
         <v>0.0338100311657898</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>3097</v>
       </c>
       <c r="AD36" t="s">
         <v>35</v>
       </c>
       <c r="AE36" t="s">
-        <v>3100</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>3100</v>
-      </c>
-      <c r="AH36" t="n">
+        <v>3097</v>
+      </c>
+      <c r="AF36" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" t="b">
+      <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="s">
-        <v>3152</v>
+      <c r="AH36" t="s">
+        <v>3149</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="D37" t="s">
         <v>29</v>
@@ -14721,59 +14621,57 @@
         <v>460761</v>
       </c>
       <c r="U37" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="V37" t="n">
         <v>78053</v>
       </c>
       <c r="W37" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
       </c>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="Y37" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z37" t="n">
         <v>-0.481025421564913</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AA37" t="n">
         <v>0.174637629873703</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>3093</v>
       </c>
       <c r="AD37" t="s">
         <v>35</v>
       </c>
       <c r="AE37" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>3096</v>
-      </c>
-      <c r="AH37" t="n">
+        <v>3093</v>
+      </c>
+      <c r="AF37" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" t="b">
+      <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>3154</v>
+      <c r="AH37" t="s">
+        <v>3151</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B38" t="s">
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>3155</v>
+        <v>3152</v>
       </c>
       <c r="D38" t="s">
         <v>22</v>
@@ -14827,62 +14725,60 @@
         <v>451866</v>
       </c>
       <c r="U38" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="V38" t="n">
         <v>111002</v>
       </c>
       <c r="W38" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AA38" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="Y38" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z38" t="n">
         <v>-0.317331341498765</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AA38" t="n">
         <v>0.144936999935182</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>3085</v>
       </c>
       <c r="AD38" t="s">
         <v>35</v>
       </c>
       <c r="AE38" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AH38" t="n">
+        <v>3085</v>
+      </c>
+      <c r="AF38" t="n">
         <v>2</v>
       </c>
-      <c r="AI38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>3156</v>
+      <c r="AG38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>3153</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B39" t="s">
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>3157</v>
+        <v>3154</v>
       </c>
       <c r="D39" t="s">
-        <v>3074</v>
+        <v>3071</v>
       </c>
       <c r="E39" t="n">
         <v>405846</v>
@@ -14933,59 +14829,57 @@
         <v>405846</v>
       </c>
       <c r="U39" t="s">
-        <v>3158</v>
+        <v>3155</v>
       </c>
       <c r="V39" t="n">
         <v>53004</v>
       </c>
       <c r="W39" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AA39" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="Y39" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z39" t="n">
         <v>-0.139369053756064</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AA39" t="n">
         <v>0.0530097983630173</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>3156</v>
       </c>
       <c r="AD39" t="s">
         <v>35</v>
       </c>
       <c r="AE39" t="s">
-        <v>3159</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>3159</v>
-      </c>
-      <c r="AH39" t="n">
+        <v>3156</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" t="b">
+      <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>3160</v>
+      <c r="AH39" t="s">
+        <v>3157</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B40" t="s">
         <v>19</v>
       </c>
       <c r="C40" t="s">
-        <v>3161</v>
+        <v>3158</v>
       </c>
       <c r="D40" t="s">
         <v>106</v>
@@ -15039,59 +14933,57 @@
         <v>444980</v>
       </c>
       <c r="U40" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="V40" t="n">
         <v>126521</v>
       </c>
       <c r="W40" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
       </c>
-      <c r="Y40"/>
-      <c r="Z40"/>
-      <c r="AA40" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="Y40" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.0719034249678417</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AA40" t="n">
         <v>0.0316057046877326</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>3073</v>
       </c>
       <c r="AD40" t="s">
         <v>35</v>
       </c>
       <c r="AE40" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>3076</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>3162</v>
+        <v>3073</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>3159</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>3163</v>
+        <v>3160</v>
       </c>
       <c r="D41" t="s">
         <v>22</v>
@@ -15145,59 +15037,57 @@
         <v>451866</v>
       </c>
       <c r="U41" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="V41" t="n">
         <v>1028071</v>
       </c>
       <c r="W41" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
       </c>
-      <c r="Y41"/>
-      <c r="Z41"/>
-      <c r="AA41" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="Y41" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.0732344853806992</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AA41" t="n">
         <v>0.0283621323156057</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>3077</v>
       </c>
       <c r="AD41" t="s">
         <v>35</v>
       </c>
       <c r="AE41" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AH41" t="n">
+        <v>3077</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" t="b">
+      <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="s">
-        <v>3164</v>
+      <c r="AH41" t="s">
+        <v>3161</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B42" t="s">
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>3165</v>
+        <v>3162</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -15251,59 +15141,57 @@
         <v>460761</v>
       </c>
       <c r="U42" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="V42" t="n">
         <v>751961</v>
       </c>
       <c r="W42" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
       </c>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AA42" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="Y42" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z42" t="n">
         <v>-0.261343175522674</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AA42" t="n">
         <v>0.11704089115795</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>3085</v>
       </c>
       <c r="AD42" t="s">
         <v>35</v>
       </c>
       <c r="AE42" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AF42" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AH42" t="n">
+        <v>3085</v>
+      </c>
+      <c r="AF42" t="n">
         <v>0</v>
       </c>
-      <c r="AI42" t="b">
+      <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="s">
-        <v>3166</v>
+      <c r="AH42" t="s">
+        <v>3163</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -15357,59 +15245,57 @@
         <v>460761</v>
       </c>
       <c r="U43" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="V43" t="n">
         <v>648640</v>
       </c>
       <c r="W43" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X43" t="b">
         <v>1</v>
       </c>
-      <c r="Y43"/>
-      <c r="Z43"/>
-      <c r="AA43" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="Y43" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.0919984042293124</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AA43" t="n">
         <v>0.0380193373975506</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>3077</v>
       </c>
       <c r="AD43" t="s">
         <v>35</v>
       </c>
       <c r="AE43" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AF43" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG43" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AH43" t="n">
+        <v>3077</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0</v>
       </c>
-      <c r="AI43" t="b">
+      <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="s">
-        <v>3168</v>
+      <c r="AH43" t="s">
+        <v>3165</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -15463,59 +15349,57 @@
         <v>460761</v>
       </c>
       <c r="U44" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V44" t="n">
         <v>254641</v>
       </c>
       <c r="W44" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X44" t="b">
         <v>1</v>
       </c>
-      <c r="Y44"/>
-      <c r="Z44"/>
-      <c r="AA44" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB44" t="n">
+      <c r="Y44" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0.0765196488641102</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AA44" t="n">
         <v>0.0321203995332098</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>3168</v>
       </c>
       <c r="AD44" t="s">
         <v>35</v>
       </c>
       <c r="AE44" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF44" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH44" t="n">
+        <v>3168</v>
+      </c>
+      <c r="AF44" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" t="b">
+      <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AJ44" t="s">
-        <v>3172</v>
+      <c r="AH44" t="s">
+        <v>3169</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B45" t="s">
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>3173</v>
+        <v>3170</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -15569,62 +15453,60 @@
         <v>451866</v>
       </c>
       <c r="U45" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
       <c r="V45" t="n">
         <v>526335</v>
       </c>
       <c r="W45" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X45" t="b">
         <v>1</v>
       </c>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB45" t="n">
+      <c r="Y45" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z45" t="n">
         <v>-0.208800705560002</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AA45" t="n">
         <v>0.0914126774276241</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>3062</v>
       </c>
       <c r="AD45" t="s">
         <v>35</v>
       </c>
       <c r="AE45" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AF45" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AH45" t="n">
+        <v>3062</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0</v>
       </c>
-      <c r="AI45" t="b">
+      <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="s">
-        <v>3174</v>
+      <c r="AH45" t="s">
+        <v>3171</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B46" t="s">
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>3175</v>
+        <v>3172</v>
       </c>
       <c r="D46" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="E46" t="n">
         <v>428479</v>
@@ -15675,62 +15557,60 @@
         <v>432288</v>
       </c>
       <c r="U46" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="V46" t="n">
         <v>1239492</v>
       </c>
       <c r="W46" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
       </c>
-      <c r="Y46"/>
-      <c r="Z46"/>
-      <c r="AA46" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB46" t="n">
+      <c r="Y46" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.0637272311757711</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AA46" t="n">
         <v>0.0278877114583524</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>3081</v>
       </c>
       <c r="AD46" t="s">
         <v>35</v>
       </c>
       <c r="AE46" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AH46" t="n">
+        <v>3081</v>
+      </c>
+      <c r="AF46" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" t="b">
+      <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="s">
-        <v>3176</v>
+      <c r="AH46" t="s">
+        <v>3173</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>3177</v>
+        <v>3174</v>
       </c>
       <c r="D47" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="E47" t="n">
         <v>382894</v>
@@ -15781,59 +15661,57 @@
         <v>432288</v>
       </c>
       <c r="U47" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
       <c r="V47" t="n">
         <v>105014</v>
       </c>
       <c r="W47" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X47" t="b">
         <v>1</v>
       </c>
-      <c r="Y47"/>
-      <c r="Z47"/>
-      <c r="AA47" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB47" t="n">
+      <c r="Y47" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z47" t="n">
         <v>-0.170631796269854</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AA47" t="n">
         <v>0.0687465426841288</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>3062</v>
       </c>
       <c r="AD47" t="s">
         <v>35</v>
       </c>
       <c r="AE47" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AH47" t="n">
+        <v>3062</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0</v>
       </c>
-      <c r="AI47" t="b">
+      <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AJ47" t="s">
-        <v>3178</v>
+      <c r="AH47" t="s">
+        <v>3175</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>3179</v>
+        <v>3176</v>
       </c>
       <c r="D48" t="s">
         <v>29</v>
@@ -15887,59 +15765,57 @@
         <v>460761</v>
       </c>
       <c r="U48" t="s">
-        <v>3158</v>
+        <v>3155</v>
       </c>
       <c r="V48" t="n">
         <v>223156</v>
       </c>
       <c r="W48" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X48" t="b">
         <v>1</v>
       </c>
-      <c r="Y48"/>
-      <c r="Z48"/>
-      <c r="AA48" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB48" t="n">
+      <c r="Y48" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.110962851093697</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AA48" t="n">
         <v>0.0470871176797533</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>3156</v>
       </c>
       <c r="AD48" t="s">
         <v>35</v>
       </c>
       <c r="AE48" t="s">
-        <v>3159</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG48" t="s">
-        <v>3159</v>
-      </c>
-      <c r="AH48" t="n">
+        <v>3156</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0</v>
       </c>
-      <c r="AI48" t="b">
+      <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="s">
-        <v>3180</v>
+      <c r="AH48" t="s">
+        <v>3177</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B49" t="s">
         <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>3181</v>
+        <v>3178</v>
       </c>
       <c r="D49" t="s">
         <v>29</v>
@@ -15993,62 +15869,60 @@
         <v>460761</v>
       </c>
       <c r="U49" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="V49" t="n">
         <v>252059</v>
       </c>
       <c r="W49" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
       </c>
-      <c r="Y49"/>
-      <c r="Z49"/>
-      <c r="AA49" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB49" t="n">
+      <c r="Y49" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z49" t="n">
         <v>-0.14614932056513</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AA49" t="n">
         <v>0.0673702301285729</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>3097</v>
       </c>
       <c r="AD49" t="s">
         <v>35</v>
       </c>
       <c r="AE49" t="s">
-        <v>3100</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG49" t="s">
-        <v>3100</v>
-      </c>
-      <c r="AH49" t="n">
+        <v>3097</v>
+      </c>
+      <c r="AF49" t="n">
         <v>0</v>
       </c>
-      <c r="AI49" t="b">
+      <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="s">
-        <v>3182</v>
+      <c r="AH49" t="s">
+        <v>3179</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B50" t="s">
         <v>19</v>
       </c>
       <c r="C50" t="s">
-        <v>3183</v>
+        <v>3180</v>
       </c>
       <c r="D50" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="E50" t="n">
         <v>415343</v>
@@ -16099,59 +15973,57 @@
         <v>428479</v>
       </c>
       <c r="U50" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="V50" t="n">
         <v>524103</v>
       </c>
       <c r="W50" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X50" t="b">
         <v>1</v>
       </c>
-      <c r="Y50"/>
-      <c r="Z50"/>
-      <c r="AA50" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="Y50" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z50" t="n">
         <v>-0.405562288603622</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AA50" t="n">
         <v>0.16881669778676</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>3056</v>
       </c>
       <c r="AD50" t="s">
         <v>35</v>
       </c>
       <c r="AE50" t="s">
-        <v>3059</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG50" t="s">
-        <v>3059</v>
-      </c>
-      <c r="AH50" t="n">
+        <v>3056</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" t="b">
+      <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="s">
-        <v>3184</v>
+      <c r="AH50" t="s">
+        <v>3181</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B51" t="s">
         <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="D51" t="s">
         <v>22</v>
@@ -16205,59 +16077,57 @@
         <v>451866</v>
       </c>
       <c r="U51" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V51" t="n">
         <v>533973</v>
       </c>
       <c r="W51" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X51" t="b">
         <v>1</v>
       </c>
-      <c r="Y51"/>
-      <c r="Z51"/>
-      <c r="AA51" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="Y51" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.0622693797691868</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AA51" t="n">
         <v>0.0258845596556136</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>3168</v>
       </c>
       <c r="AD51" t="s">
         <v>35</v>
       </c>
       <c r="AE51" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF51" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG51" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH51" t="n">
+        <v>3168</v>
+      </c>
+      <c r="AF51" t="n">
         <v>0</v>
       </c>
-      <c r="AI51" t="b">
+      <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="s">
-        <v>3186</v>
+      <c r="AH51" t="s">
+        <v>3183</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B52" t="s">
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>3187</v>
+        <v>3184</v>
       </c>
       <c r="D52" t="s">
         <v>106</v>
@@ -16311,59 +16181,57 @@
         <v>444980</v>
       </c>
       <c r="U52" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V52" t="n">
         <v>369547</v>
       </c>
       <c r="W52" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X52" t="b">
         <v>1</v>
       </c>
-      <c r="Y52"/>
-      <c r="Z52"/>
-      <c r="AA52" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="Y52" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z52" t="n">
         <v>-0.0615657683849028</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AA52" t="n">
         <v>0.0266495233630782</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>3067</v>
       </c>
       <c r="AD52" t="s">
         <v>35</v>
       </c>
       <c r="AE52" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF52" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG52" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH52" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF52" t="n">
         <v>0</v>
       </c>
-      <c r="AI52" t="b">
+      <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AJ52" t="s">
-        <v>3188</v>
+      <c r="AH52" t="s">
+        <v>3185</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B53" t="s">
         <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>3189</v>
+        <v>3186</v>
       </c>
       <c r="D53" t="s">
         <v>29</v>
@@ -16417,59 +16285,57 @@
         <v>460761</v>
       </c>
       <c r="U53" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="V53" t="n">
         <v>818827</v>
       </c>
       <c r="W53" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X53" t="b">
         <v>1</v>
       </c>
-      <c r="Y53"/>
-      <c r="Z53"/>
-      <c r="AA53" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB53" t="n">
+      <c r="Y53" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z53" t="n">
         <v>-0.394686443746397</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AA53" t="n">
         <v>0.191605708966359</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>3085</v>
       </c>
       <c r="AD53" t="s">
         <v>35</v>
       </c>
       <c r="AE53" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG53" t="s">
-        <v>3088</v>
-      </c>
-      <c r="AH53" t="n">
+        <v>3085</v>
+      </c>
+      <c r="AF53" t="n">
         <v>0</v>
       </c>
-      <c r="AI53" t="b">
+      <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AJ53" t="s">
-        <v>3190</v>
+      <c r="AH53" t="s">
+        <v>3187</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
       </c>
       <c r="C54" t="s">
-        <v>3191</v>
+        <v>3188</v>
       </c>
       <c r="D54" t="s">
         <v>29</v>
@@ -16523,59 +16389,57 @@
         <v>460761</v>
       </c>
       <c r="U54" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V54" t="n">
         <v>23935</v>
       </c>
       <c r="W54" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X54" t="b">
         <v>1</v>
       </c>
-      <c r="Y54"/>
-      <c r="Z54"/>
-      <c r="AA54" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB54" t="n">
+      <c r="Y54" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z54" t="n">
         <v>-0.199910978389123</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AA54" t="n">
         <v>0.0828071033102391</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>3168</v>
       </c>
       <c r="AD54" t="s">
         <v>35</v>
       </c>
       <c r="AE54" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF54" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG54" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH54" t="n">
+        <v>3168</v>
+      </c>
+      <c r="AF54" t="n">
         <v>0</v>
       </c>
-      <c r="AI54" t="b">
+      <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AJ54" t="s">
-        <v>3192</v>
+      <c r="AH54" t="s">
+        <v>3189</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
       </c>
       <c r="C55" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
       <c r="D55" t="s">
         <v>29</v>
@@ -16629,62 +16493,60 @@
         <v>460761</v>
       </c>
       <c r="U55" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="V55" t="n">
         <v>117664</v>
       </c>
       <c r="W55" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X55" t="b">
         <v>1</v>
       </c>
-      <c r="Y55"/>
-      <c r="Z55"/>
-      <c r="AA55" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="Y55" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.0696454499618102</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AA55" t="n">
         <v>0.0287998902463806</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>3081</v>
       </c>
       <c r="AD55" t="s">
         <v>35</v>
       </c>
       <c r="AE55" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AF55" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG55" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AH55" t="n">
+        <v>3081</v>
+      </c>
+      <c r="AF55" t="n">
         <v>0</v>
       </c>
-      <c r="AI55" t="b">
+      <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AJ55" t="s">
-        <v>3194</v>
+      <c r="AH55" t="s">
+        <v>3191</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
       </c>
       <c r="C56" t="s">
-        <v>3195</v>
+        <v>3192</v>
       </c>
       <c r="D56" t="s">
-        <v>3074</v>
+        <v>3071</v>
       </c>
       <c r="E56" t="n">
         <v>382894</v>
@@ -16735,59 +16597,57 @@
         <v>405846</v>
       </c>
       <c r="U56" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V56" t="n">
         <v>231519</v>
       </c>
       <c r="W56" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X56" t="b">
         <v>1</v>
       </c>
-      <c r="Y56"/>
-      <c r="Z56"/>
-      <c r="AA56" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB56" t="n">
+      <c r="Y56" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z56" t="n">
         <v>0.120471417418127</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AA56" t="n">
         <v>0.0474037924606281</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>3067</v>
       </c>
       <c r="AD56" t="s">
         <v>35</v>
       </c>
       <c r="AE56" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF56" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG56" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH56" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF56" t="n">
         <v>0</v>
       </c>
-      <c r="AI56" t="b">
+      <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="s">
-        <v>3196</v>
+      <c r="AH56" t="s">
+        <v>3193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B57" t="s">
         <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>3197</v>
+        <v>3194</v>
       </c>
       <c r="D57" t="s">
         <v>29</v>
@@ -16841,59 +16701,57 @@
         <v>460761</v>
       </c>
       <c r="U57" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V57" t="n">
         <v>866224</v>
       </c>
       <c r="W57" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X57" t="b">
         <v>1</v>
       </c>
-      <c r="Y57"/>
-      <c r="Z57"/>
-      <c r="AA57" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB57" t="n">
+      <c r="Y57" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z57" t="n">
         <v>-0.396681351192431</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AA57" t="n">
         <v>0.165081091484867</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>3168</v>
       </c>
       <c r="AD57" t="s">
         <v>35</v>
       </c>
       <c r="AE57" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF57" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG57" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH57" t="n">
+        <v>3168</v>
+      </c>
+      <c r="AF57" t="n">
         <v>0</v>
       </c>
-      <c r="AI57" t="b">
+      <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="s">
-        <v>3198</v>
+      <c r="AH57" t="s">
+        <v>3195</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>3199</v>
+        <v>3196</v>
       </c>
       <c r="D58" t="s">
         <v>106</v>
@@ -16947,59 +16805,57 @@
         <v>444980</v>
       </c>
       <c r="U58" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="V58" t="n">
         <v>916486</v>
       </c>
       <c r="W58" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X58" t="b">
         <v>1</v>
       </c>
-      <c r="Y58"/>
-      <c r="Z58"/>
-      <c r="AA58" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB58" t="n">
+      <c r="Y58" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z58" t="n">
         <v>-0.193227491968968</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AA58" t="n">
         <v>0.0778390854239845</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>3081</v>
       </c>
       <c r="AD58" t="s">
         <v>35</v>
       </c>
       <c r="AE58" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AF58" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG58" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AH58" t="n">
+        <v>3081</v>
+      </c>
+      <c r="AF58" t="n">
         <v>0</v>
       </c>
-      <c r="AI58" t="b">
+      <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="s">
-        <v>3200</v>
+      <c r="AH58" t="s">
+        <v>3197</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B59" t="s">
         <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>3201</v>
+        <v>3198</v>
       </c>
       <c r="D59" t="s">
         <v>29</v>
@@ -17053,62 +16909,60 @@
         <v>460761</v>
       </c>
       <c r="U59" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="V59" t="n">
         <v>1059531</v>
       </c>
       <c r="W59" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X59" t="b">
         <v>1</v>
       </c>
-      <c r="Y59"/>
-      <c r="Z59"/>
-      <c r="AA59" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB59" t="n">
+      <c r="Y59" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z59" t="n">
         <v>-0.340694948583608</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AA59" t="n">
         <v>0.133117192105593</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>3077</v>
       </c>
       <c r="AD59" t="s">
         <v>35</v>
       </c>
       <c r="AE59" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AF59" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG59" t="s">
-        <v>3080</v>
-      </c>
-      <c r="AH59" t="n">
+        <v>3077</v>
+      </c>
+      <c r="AF59" t="n">
         <v>0</v>
       </c>
-      <c r="AI59" t="b">
+      <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="s">
-        <v>3202</v>
+      <c r="AH59" t="s">
+        <v>3199</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B60" t="s">
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>3203</v>
+        <v>3200</v>
       </c>
       <c r="D60" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="E60" t="n">
         <v>376755</v>
@@ -17159,59 +17013,57 @@
         <v>432288</v>
       </c>
       <c r="U60" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V60" t="n">
         <v>912824</v>
       </c>
       <c r="W60" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X60" t="b">
         <v>1</v>
       </c>
-      <c r="Y60"/>
-      <c r="Z60"/>
-      <c r="AA60" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB60" t="n">
+      <c r="Y60" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z60" t="n">
         <v>0.124783406959899</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AA60" t="n">
         <v>0.0511746123401526</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>3168</v>
       </c>
       <c r="AD60" t="s">
         <v>35</v>
       </c>
       <c r="AE60" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF60" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG60" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH60" t="n">
+        <v>3168</v>
+      </c>
+      <c r="AF60" t="n">
         <v>0</v>
       </c>
-      <c r="AI60" t="b">
+      <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="s">
-        <v>3204</v>
+      <c r="AH60" t="s">
+        <v>3201</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B61" t="s">
         <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>3205</v>
+        <v>3202</v>
       </c>
       <c r="D61" t="s">
         <v>29</v>
@@ -17265,59 +17117,57 @@
         <v>460761</v>
       </c>
       <c r="U61" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V61" t="n">
         <v>226399</v>
       </c>
       <c r="W61" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X61" t="b">
         <v>1</v>
       </c>
-      <c r="Y61"/>
-      <c r="Z61"/>
-      <c r="AA61" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB61" t="n">
+      <c r="Y61" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z61" t="n">
         <v>-0.216089488762741</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AA61" t="n">
         <v>0.104245505081007</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>3168</v>
       </c>
       <c r="AD61" t="s">
         <v>35</v>
       </c>
       <c r="AE61" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF61" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG61" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH61" t="n">
+        <v>3168</v>
+      </c>
+      <c r="AF61" t="n">
         <v>0</v>
       </c>
-      <c r="AI61" t="b">
+      <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="s">
-        <v>3206</v>
+      <c r="AH61" t="s">
+        <v>3203</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B62" t="s">
         <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>3207</v>
+        <v>3204</v>
       </c>
       <c r="D62" t="s">
         <v>29</v>
@@ -17371,62 +17221,60 @@
         <v>460761</v>
       </c>
       <c r="U62" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="V62" t="n">
         <v>491515</v>
       </c>
       <c r="W62" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X62" t="b">
         <v>1</v>
       </c>
-      <c r="Y62"/>
-      <c r="Z62"/>
-      <c r="AA62" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB62" t="n">
+      <c r="Y62" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z62" t="n">
         <v>-0.129154295366272</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AA62" t="n">
         <v>0.0519556300767174</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>3081</v>
       </c>
       <c r="AD62" t="s">
         <v>35</v>
       </c>
       <c r="AE62" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AF62" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG62" t="s">
-        <v>3084</v>
-      </c>
-      <c r="AH62" t="n">
+        <v>3081</v>
+      </c>
+      <c r="AF62" t="n">
         <v>0</v>
       </c>
-      <c r="AI62" t="b">
+      <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="s">
-        <v>3208</v>
+      <c r="AH62" t="s">
+        <v>3205</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B63" t="s">
         <v>19</v>
       </c>
       <c r="C63" t="s">
-        <v>3209</v>
+        <v>3206</v>
       </c>
       <c r="D63" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="E63" t="n">
         <v>428479</v>
@@ -17477,59 +17325,57 @@
         <v>432288</v>
       </c>
       <c r="U63" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="V63" t="n">
         <v>712319</v>
       </c>
       <c r="W63" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="X63" t="b">
         <v>1</v>
       </c>
-      <c r="Y63"/>
-      <c r="Z63"/>
-      <c r="AA63" t="s">
-        <v>3058</v>
-      </c>
-      <c r="AB63" t="n">
+      <c r="Y63" t="s">
+        <v>3055</v>
+      </c>
+      <c r="Z63" t="n">
         <v>0.0730374815133528</v>
       </c>
-      <c r="AC63" t="n">
+      <c r="AA63" t="n">
         <v>0.0330100176692085</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>3067</v>
       </c>
       <c r="AD63" t="s">
         <v>35</v>
       </c>
       <c r="AE63" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AF63" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG63" t="s">
-        <v>3070</v>
-      </c>
-      <c r="AH63" t="n">
+        <v>3067</v>
+      </c>
+      <c r="AF63" t="n">
         <v>0</v>
       </c>
-      <c r="AI63" t="b">
+      <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="s">
-        <v>3210</v>
+      <c r="AH63" t="s">
+        <v>3207</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B64" t="s">
         <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>3211</v>
+        <v>3208</v>
       </c>
       <c r="D64" t="s">
         <v>29</v>
@@ -17583,48 +17429,46 @@
         <v>460761</v>
       </c>
       <c r="U64" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
       <c r="V64" t="n">
         <v>608305</v>
       </c>
       <c r="W64" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="X64" t="b">
         <v>1</v>
       </c>
-      <c r="Y64"/>
-      <c r="Z64"/>
-      <c r="AA64" t="s">
-        <v>3064</v>
-      </c>
-      <c r="AB64" t="n">
+      <c r="Y64" t="s">
+        <v>3061</v>
+      </c>
+      <c r="Z64" t="n">
         <v>0.0656437779484341</v>
       </c>
-      <c r="AC64" t="n">
+      <c r="AA64" t="n">
         <v>0.0365189543955355</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>3062</v>
       </c>
       <c r="AD64" t="s">
         <v>35</v>
       </c>
       <c r="AE64" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AF64" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG64" t="s">
-        <v>3065</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ64" t="s">
-        <v>3212</v>
+        <v>3062</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>3209</v>
       </c>
     </row>
   </sheetData>
@@ -17703,37 +17547,28 @@
         <v>3041</v>
       </c>
       <c r="V1" t="s">
-        <v>3213</v>
+        <v>53</v>
       </c>
       <c r="W1" t="s">
-        <v>3214</v>
+        <v>3044</v>
       </c>
       <c r="X1" t="s">
-        <v>3215</v>
+        <v>3045</v>
       </c>
       <c r="Y1" t="s">
-        <v>3216</v>
+        <v>3046</v>
       </c>
       <c r="Z1" t="s">
-        <v>3217</v>
+        <v>33</v>
       </c>
       <c r="AA1" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="AB1" t="s">
-        <v>3049</v>
+        <v>3210</v>
       </c>
       <c r="AC1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3050</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3218</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3053</v>
       </c>
     </row>
     <row r="2">
@@ -17741,10 +17576,10 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>3219</v>
+        <v>3211</v>
       </c>
       <c r="C2" t="s">
-        <v>3220</v>
+        <v>3212</v>
       </c>
       <c r="D2" t="n">
         <v>481310</v>
@@ -17801,37 +17636,28 @@
         <v>480535</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.73309196089202</v>
+        <v>-1.17798062457302</v>
       </c>
       <c r="W2" t="n">
-        <v>-4.42634852720014</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-4.56637526738435</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1.0646031776306</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-3.0623492680388</v>
+        <v>0.308490553318007</v>
+      </c>
+      <c r="X2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>35</v>
       </c>
       <c r="AA2" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" t="s">
-        <v>35</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3221</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="3">
@@ -17839,7 +17665,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>3222</v>
+        <v>3214</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
@@ -17899,37 +17725,28 @@
         <v>451464</v>
       </c>
       <c r="V3" t="n">
-        <v>-4.16206335015615</v>
+        <v>-0.459019765602908</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.82579792360466</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-4.65672182709227</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-2.9143414911421</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-2.84908485590753</v>
+        <v>0.128369969227783</v>
+      </c>
+      <c r="X3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>35</v>
       </c>
       <c r="AA3" t="s">
         <v>35</v>
       </c>
-      <c r="AB3" t="s">
-        <v>35</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="4">
@@ -17937,10 +17754,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>3224</v>
+        <v>3216</v>
       </c>
       <c r="C4" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="D4" t="n">
         <v>428479</v>
@@ -17997,37 +17814,28 @@
         <v>428650</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.13700257216243</v>
+        <v>-0.774091576729772</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.03233418831589</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.71178774046361</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.03606232962451</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-3.71485229987723</v>
+        <v>0.332166097776187</v>
+      </c>
+      <c r="X4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>35</v>
       </c>
       <c r="AA4" t="s">
         <v>35</v>
       </c>
-      <c r="AB4" t="s">
-        <v>35</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3225</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="5">
@@ -18035,10 +17843,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="C5" t="s">
-        <v>3227</v>
+        <v>3219</v>
       </c>
       <c r="D5" t="n">
         <v>582788</v>
@@ -18095,37 +17903,28 @@
         <v>406636</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.21170974742879</v>
+        <v>-0.0890963694261177</v>
       </c>
       <c r="W5" t="n">
-        <v>-3.24500013720044</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-2.74277400675796</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2.0891344811719</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-2.99237935681394</v>
+        <v>0.0331967398486981</v>
+      </c>
+      <c r="X5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>35</v>
       </c>
       <c r="AA5" t="s">
         <v>35</v>
       </c>
-      <c r="AB5" t="s">
-        <v>35</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3228</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="6">
@@ -18133,10 +17932,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>3229</v>
+        <v>3221</v>
       </c>
       <c r="C6" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="D6" t="n">
         <v>428479</v>
@@ -18193,37 +17992,28 @@
         <v>457015</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.836932936922129</v>
+        <v>-0.274100913739397</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.50939743746597</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.16847417116219</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-3.54508519683863</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-1.88207546242747</v>
+        <v>0.16838023478588</v>
+      </c>
+      <c r="X6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>35</v>
       </c>
       <c r="AA6" t="s">
         <v>35</v>
       </c>
-      <c r="AB6" t="s">
-        <v>35</v>
+      <c r="AB6" t="n">
+        <v>0.00078740157480315</v>
       </c>
       <c r="AC6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.00078740157480315</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3230</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="7">
@@ -18231,10 +18021,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="C7" t="s">
-        <v>3232</v>
+        <v>3224</v>
       </c>
       <c r="D7" t="n">
         <v>920406</v>
@@ -18291,37 +18081,28 @@
         <v>404950</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.472248114182124</v>
+        <v>0.183676057261263</v>
       </c>
       <c r="W7" t="n">
-        <v>1.76762612079051</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.40735239360315</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.60210230678772</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-1.43260072281387</v>
+        <v>0.149257187531112</v>
+      </c>
+      <c r="X7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>35</v>
       </c>
       <c r="AA7" t="s">
         <v>35</v>
       </c>
-      <c r="AB7" t="s">
-        <v>35</v>
+      <c r="AB7" t="n">
+        <v>0.00120481927710843</v>
       </c>
       <c r="AC7" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.00120481927710843</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="8">
@@ -18329,10 +18110,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="C8" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="D8" t="n">
         <v>382894</v>
@@ -18389,37 +18170,28 @@
         <v>425164</v>
       </c>
       <c r="V8" t="n">
-        <v>2.98751281367726</v>
+        <v>0.832792992405044</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47286724392132</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.55016527968969</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.75515487074153</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.36023113891093</v>
+        <v>0.367422466292206</v>
+      </c>
+      <c r="X8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>35</v>
       </c>
       <c r="AA8" t="s">
         <v>35</v>
       </c>
-      <c r="AB8" t="s">
-        <v>35</v>
+      <c r="AB8" t="n">
+        <v>0.00120481927710843</v>
       </c>
       <c r="AC8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.00120481927710843</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="9">
@@ -18427,7 +18199,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -18487,37 +18259,28 @@
         <v>462361</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.54646653461245</v>
+        <v>-0.52169023061849</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.12568602672533</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.716534159546792</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.370949344534737</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-3.11525986599692</v>
+        <v>0.32866055730714</v>
+      </c>
+      <c r="X9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>35</v>
       </c>
       <c r="AA9" t="s">
         <v>35</v>
       </c>
-      <c r="AB9" t="s">
-        <v>35</v>
+      <c r="AB9" t="n">
+        <v>0.00120481927710843</v>
       </c>
       <c r="AC9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.00120481927710843</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="10">
@@ -18525,10 +18288,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
       <c r="C10" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
       <c r="D10" t="n">
         <v>524953</v>
@@ -18585,37 +18348,28 @@
         <v>383455</v>
       </c>
       <c r="V10" t="n">
-        <v>2.78638467630582</v>
+        <v>0.326817523048645</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0186895986011264</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.35371303230315</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.938092088214153</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.79094917205558</v>
+        <v>0.169628964027951</v>
+      </c>
+      <c r="X10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>35</v>
       </c>
       <c r="AA10" t="s">
         <v>35</v>
       </c>
-      <c r="AB10" t="s">
-        <v>35</v>
+      <c r="AB10" t="n">
+        <v>0.00330110603151047</v>
       </c>
       <c r="AC10" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.00330110603151047</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="11">
@@ -18623,10 +18377,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
       <c r="C11" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="D11" t="n">
         <v>408265</v>
@@ -18683,37 +18437,28 @@
         <v>418512</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.50689901117266</v>
+        <v>-0.664407637540851</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.4852484179654</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-2.34356945432487</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-1.63295951965637</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.519895615244322</v>
+        <v>0.418327083316769</v>
+      </c>
+      <c r="X11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>35</v>
       </c>
       <c r="AA11" t="s">
         <v>35</v>
       </c>
-      <c r="AB11" t="s">
-        <v>35</v>
+      <c r="AB11" t="n">
+        <v>0.0037914691943128</v>
       </c>
       <c r="AC11" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.0037914691943128</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>3242</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="12">
@@ -18721,10 +18466,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="C12" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="D12" t="n">
         <v>147305</v>
@@ -18781,37 +18526,28 @@
         <v>479225</v>
       </c>
       <c r="V12" t="n">
-        <v>0.730143765862464</v>
+        <v>0.0572812280271456</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.43913039672481</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.410323590884198</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-2.32437946625984</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.8031025601235</v>
+        <v>0.347085256204455</v>
+      </c>
+      <c r="X12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>35</v>
       </c>
       <c r="AA12" t="s">
         <v>35</v>
       </c>
-      <c r="AB12" t="s">
-        <v>35</v>
+      <c r="AB12" t="n">
+        <v>0.00409090909090909</v>
       </c>
       <c r="AC12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.00409090909090909</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="13">
@@ -18819,7 +18555,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>3245</v>
+        <v>3237</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -18879,37 +18615,28 @@
         <v>410443</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.87229514858699</v>
+        <v>-0.787125331914157</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.751453777190131</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-1.6475870077412</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-2.38115988087635</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-2.38902302362118</v>
+        <v>0.460457427954336</v>
+      </c>
+      <c r="X13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>35</v>
       </c>
       <c r="AA13" t="s">
         <v>35</v>
       </c>
-      <c r="AB13" t="s">
-        <v>35</v>
+      <c r="AB13" t="n">
+        <v>0.00409090909090909</v>
       </c>
       <c r="AC13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.00409090909090909</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="14">
@@ -18917,10 +18644,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="C14" t="s">
-        <v>3248</v>
+        <v>3240</v>
       </c>
       <c r="D14" t="n">
         <v>193935</v>
@@ -18977,37 +18704,28 @@
         <v>472920</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.50758071638667</v>
+        <v>-0.260462681030812</v>
       </c>
       <c r="W14" t="n">
-        <v>0.312516440049025</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.44161687156717</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-3.81381554373948</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.212416779338946</v>
+        <v>0.255507983022437</v>
+      </c>
+      <c r="X14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>35</v>
       </c>
       <c r="AA14" t="s">
         <v>35</v>
       </c>
-      <c r="AB14" t="s">
-        <v>35</v>
+      <c r="AB14" t="n">
+        <v>0.00448430493273543</v>
       </c>
       <c r="AC14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.00448430493273543</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>3249</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="15">
@@ -19015,10 +18733,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>3250</v>
+        <v>3242</v>
       </c>
       <c r="C15" t="s">
-        <v>3251</v>
+        <v>3243</v>
       </c>
       <c r="D15" t="n">
         <v>115128</v>
@@ -19075,37 +18793,28 @@
         <v>394038</v>
       </c>
       <c r="V15" t="n">
-        <v>1.56325626190981</v>
+        <v>0.257979086129292</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.1111873740948</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.52459401773769</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25436947499585</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>-1.5299443882143</v>
+        <v>0.306131798872554</v>
+      </c>
+      <c r="X15" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>35</v>
       </c>
       <c r="AA15" t="s">
         <v>35</v>
       </c>
-      <c r="AB15" t="s">
-        <v>35</v>
+      <c r="AB15" t="n">
+        <v>0.00753138075313808</v>
       </c>
       <c r="AC15" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.00753138075313808</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>3252</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="16">
@@ -19113,7 +18822,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>3253</v>
+        <v>3245</v>
       </c>
       <c r="C16" t="s">
         <v>29</v>
@@ -19173,37 +18882,28 @@
         <v>464401</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.02751519380095</v>
+        <v>-0.160145442002461</v>
       </c>
       <c r="W16" t="n">
-        <v>-3.04397098700128</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-2.09260917031486</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>-1.44111875645533</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.0929923048458319</v>
+        <v>0.0924045156694907</v>
+      </c>
+      <c r="X16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>35</v>
       </c>
       <c r="AA16" t="s">
         <v>35</v>
       </c>
-      <c r="AB16" t="s">
-        <v>35</v>
+      <c r="AB16" t="n">
+        <v>0.0110236220472441</v>
       </c>
       <c r="AC16" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.0110236220472441</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>3254</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="17">
@@ -19211,10 +18911,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>3255</v>
+        <v>3247</v>
       </c>
       <c r="C17" t="s">
-        <v>3256</v>
+        <v>3248</v>
       </c>
       <c r="D17" t="n">
         <v>106953</v>
@@ -19271,37 +18971,28 @@
         <v>453921</v>
       </c>
       <c r="V17" t="n">
-        <v>2.73091416388897</v>
+        <v>-0.19397079180525</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.01658867044753</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-3.03614843472358</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.424139290506003</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-0.255769586212229</v>
+        <v>0.529968871830011</v>
+      </c>
+      <c r="X17" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>35</v>
       </c>
       <c r="AA17" t="s">
         <v>35</v>
       </c>
-      <c r="AB17" t="s">
-        <v>35</v>
+      <c r="AB17" t="n">
+        <v>0.0128866123748064</v>
       </c>
       <c r="AC17" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.0128866123748064</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="18">
@@ -19309,10 +19000,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="C18" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="D18" t="n">
         <v>87058</v>
@@ -19369,37 +19060,28 @@
         <v>460659</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.45927900770203</v>
+        <v>-0.243894914729466</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.93453428284543</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.605794113545398</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.986426387439468</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-1.44558674574643</v>
+        <v>0.215555375833024</v>
+      </c>
+      <c r="X18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>35</v>
       </c>
       <c r="AA18" t="s">
         <v>35</v>
       </c>
-      <c r="AB18" t="s">
-        <v>35</v>
+      <c r="AB18" t="n">
+        <v>0.0208547127773185</v>
       </c>
       <c r="AC18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.0208547127773185</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>3260</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="19">
@@ -19407,10 +19089,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="C19" t="s">
-        <v>3262</v>
+        <v>3254</v>
       </c>
       <c r="D19" t="n">
         <v>95370</v>
@@ -19467,37 +19149,28 @@
         <v>481319</v>
       </c>
       <c r="V19" t="n">
-        <v>0.24841053868722</v>
+        <v>-0.0742526788937747</v>
       </c>
       <c r="W19" t="n">
-        <v>-2.18711607393401</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-3.30067841846628</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>-0.658786181826131</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>-1.11437182288017</v>
+        <v>0.0509652508725601</v>
+      </c>
+      <c r="X19" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>35</v>
       </c>
       <c r="AA19" t="s">
         <v>35</v>
       </c>
-      <c r="AB19" t="s">
-        <v>35</v>
+      <c r="AB19" t="n">
+        <v>0.0268535013060251</v>
       </c>
       <c r="AC19" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.0268535013060251</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="20">
@@ -19505,10 +19178,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="C20" t="s">
-        <v>3265</v>
+        <v>3257</v>
       </c>
       <c r="D20" t="n">
         <v>48913</v>
@@ -19565,37 +19238,28 @@
         <v>420948</v>
       </c>
       <c r="V20" t="n">
-        <v>0.861632935989038</v>
+        <v>-0.0115033817569503</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.05551448009404</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.52677783164052</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>-3.23553238292612</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>-0.0513481472213182</v>
+        <v>0.357962576187284</v>
+      </c>
+      <c r="X20" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>35</v>
       </c>
       <c r="AA20" t="s">
         <v>35</v>
       </c>
-      <c r="AB20" t="s">
-        <v>35</v>
+      <c r="AB20" t="n">
+        <v>0.0288662954050584</v>
       </c>
       <c r="AC20" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.0288662954050584</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>3266</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="21">
@@ -19603,10 +19267,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="C21" t="s">
-        <v>3268</v>
+        <v>3260</v>
       </c>
       <c r="D21" t="n">
         <v>182927</v>
@@ -19663,37 +19327,28 @@
         <v>422761</v>
       </c>
       <c r="V21" t="n">
-        <v>2.65290132130744</v>
+        <v>0.0820955516335029</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0923896815516968</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-2.92795226333563</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.653337625586919</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0.41889294090698</v>
+        <v>0.327905571888236</v>
+      </c>
+      <c r="X21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>35</v>
       </c>
       <c r="AA21" t="s">
         <v>35</v>
       </c>
-      <c r="AB21" t="s">
-        <v>35</v>
+      <c r="AB21" t="n">
+        <v>0.0341472269394228</v>
       </c>
       <c r="AC21" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.0341472269394228</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>3269</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="22">
@@ -19701,10 +19356,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>3270</v>
+        <v>3262</v>
       </c>
       <c r="C22" t="s">
-        <v>3271</v>
+        <v>3263</v>
       </c>
       <c r="D22" t="n">
         <v>298438</v>
@@ -19761,37 +19416,28 @@
         <v>467260</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.25156762617012</v>
+        <v>-0.569688726438581</v>
       </c>
       <c r="W22" t="n">
-        <v>0.534559252446492</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-1.12539476889411</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>-0.929570129245048</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-0.99175707391235</v>
+        <v>0.532002363057054</v>
+      </c>
+      <c r="X22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>35</v>
       </c>
       <c r="AA22" t="s">
         <v>35</v>
       </c>
-      <c r="AB22" t="s">
-        <v>35</v>
+      <c r="AB22" t="n">
+        <v>0.037562144224294</v>
       </c>
       <c r="AC22" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.037562144224294</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>3272</v>
+        <v>3264</v>
       </c>
     </row>
   </sheetData>
@@ -19822,34 +19468,34 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3273</v>
+        <v>3265</v>
       </c>
       <c r="G1" t="s">
         <v>1564</v>
       </c>
       <c r="H1" t="s">
-        <v>3274</v>
+        <v>3266</v>
       </c>
       <c r="I1" t="s">
-        <v>3275</v>
+        <v>3267</v>
       </c>
       <c r="J1" t="s">
         <v>1621</v>
       </c>
       <c r="K1" t="s">
-        <v>3276</v>
+        <v>3268</v>
       </c>
       <c r="L1" t="s">
-        <v>3277</v>
+        <v>3269</v>
       </c>
       <c r="M1" t="s">
-        <v>3278</v>
+        <v>3270</v>
       </c>
       <c r="N1" t="s">
-        <v>3279</v>
+        <v>3271</v>
       </c>
       <c r="O1" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="P1" t="s">
         <v>3041</v>
@@ -19869,30 +19515,30 @@
         <v>1029</v>
       </c>
       <c r="E2" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F2" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G2" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3283</v>
+        <v>3275</v>
       </c>
       <c r="K2" t="s">
-        <v>3284</v>
+        <v>3276</v>
       </c>
       <c r="L2" t="s">
-        <v>3283</v>
+        <v>3275</v>
       </c>
       <c r="M2" t="s">
-        <v>3285</v>
+        <v>3277</v>
       </c>
       <c r="N2" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O2"/>
       <c r="P2" t="n">
@@ -19913,33 +19559,33 @@
         <v>954</v>
       </c>
       <c r="E3" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F3" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G3" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
       <c r="K3" t="s">
-        <v>3287</v>
+        <v>3279</v>
       </c>
       <c r="L3" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
       <c r="M3" t="s">
-        <v>3288</v>
+        <v>3280</v>
       </c>
       <c r="N3" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O3" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
       <c r="P3" t="n">
         <v>383932</v>
@@ -19959,33 +19605,33 @@
         <v>1674</v>
       </c>
       <c r="E4" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F4" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G4" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3291</v>
+        <v>3283</v>
       </c>
       <c r="K4" t="s">
-        <v>3292</v>
+        <v>3284</v>
       </c>
       <c r="L4" t="s">
-        <v>3291</v>
+        <v>3283</v>
       </c>
       <c r="M4" t="s">
-        <v>3293</v>
+        <v>3285</v>
       </c>
       <c r="N4" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O4" t="s">
-        <v>3294</v>
+        <v>3286</v>
       </c>
       <c r="P4" t="n">
         <v>385610</v>
@@ -20005,33 +19651,33 @@
         <v>6588</v>
       </c>
       <c r="E5" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F5" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G5" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3295</v>
+        <v>3287</v>
       </c>
       <c r="K5" t="s">
-        <v>3296</v>
+        <v>3288</v>
       </c>
       <c r="L5" t="s">
-        <v>3295</v>
+        <v>3287</v>
       </c>
       <c r="M5" t="s">
-        <v>3297</v>
+        <v>3289</v>
       </c>
       <c r="N5" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O5" t="s">
-        <v>3298</v>
+        <v>3290</v>
       </c>
       <c r="P5" t="n">
         <v>390360</v>
@@ -20051,33 +19697,33 @@
         <v>2535</v>
       </c>
       <c r="E6" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F6" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G6" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3250</v>
+        <v>3242</v>
       </c>
       <c r="K6" t="s">
-        <v>3299</v>
+        <v>3291</v>
       </c>
       <c r="L6" t="s">
-        <v>3250</v>
+        <v>3242</v>
       </c>
       <c r="M6" t="s">
-        <v>3300</v>
+        <v>3292</v>
       </c>
       <c r="N6" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O6" t="s">
-        <v>3252</v>
+        <v>3244</v>
       </c>
       <c r="P6" t="n">
         <v>395305</v>
@@ -20097,33 +19743,33 @@
         <v>1404</v>
       </c>
       <c r="E7" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F7" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G7" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3301</v>
+        <v>3293</v>
       </c>
       <c r="K7" t="s">
-        <v>3302</v>
+        <v>3294</v>
       </c>
       <c r="L7" t="s">
-        <v>3301</v>
+        <v>3293</v>
       </c>
       <c r="M7" t="s">
-        <v>3303</v>
+        <v>3295</v>
       </c>
       <c r="N7" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O7" t="s">
-        <v>3304</v>
+        <v>3296</v>
       </c>
       <c r="P7" t="n">
         <v>397404</v>
@@ -20143,33 +19789,33 @@
         <v>5604</v>
       </c>
       <c r="E8" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F8" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G8" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3305</v>
+        <v>3297</v>
       </c>
       <c r="K8" t="s">
-        <v>3306</v>
+        <v>3298</v>
       </c>
       <c r="L8" t="s">
-        <v>3305</v>
+        <v>3297</v>
       </c>
       <c r="M8" t="s">
-        <v>3307</v>
+        <v>3299</v>
       </c>
       <c r="N8" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O8" t="s">
-        <v>3308</v>
+        <v>3300</v>
       </c>
       <c r="P8" t="n">
         <v>401282</v>
@@ -20189,33 +19835,33 @@
         <v>1095</v>
       </c>
       <c r="E9" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F9" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G9" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="K9" t="s">
-        <v>3309</v>
+        <v>3301</v>
       </c>
       <c r="L9" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="M9" t="s">
-        <v>3310</v>
+        <v>3302</v>
       </c>
       <c r="N9" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O9" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="P9" t="n">
         <v>405497</v>
@@ -20235,30 +19881,30 @@
         <v>327</v>
       </c>
       <c r="E10" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F10" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G10" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3311</v>
+        <v>3303</v>
       </c>
       <c r="K10" t="s">
-        <v>3312</v>
+        <v>3304</v>
       </c>
       <c r="L10" t="s">
-        <v>3311</v>
+        <v>3303</v>
       </c>
       <c r="M10" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N10" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
@@ -20279,33 +19925,33 @@
         <v>904</v>
       </c>
       <c r="E11" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F11" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G11" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="K11" t="s">
-        <v>3314</v>
+        <v>3306</v>
       </c>
       <c r="L11" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="M11" t="s">
-        <v>3315</v>
+        <v>3307</v>
       </c>
       <c r="N11" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O11" t="s">
-        <v>3228</v>
+        <v>3220</v>
       </c>
       <c r="P11" t="n">
         <v>407088</v>
@@ -20325,33 +19971,33 @@
         <v>735</v>
       </c>
       <c r="E12" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F12" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G12" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>3316</v>
+        <v>3308</v>
       </c>
       <c r="K12" t="s">
-        <v>3317</v>
+        <v>3309</v>
       </c>
       <c r="L12" t="s">
-        <v>3316</v>
+        <v>3308</v>
       </c>
       <c r="M12" t="s">
-        <v>3318</v>
+        <v>3310</v>
       </c>
       <c r="N12" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O12" t="s">
-        <v>3319</v>
+        <v>3311</v>
       </c>
       <c r="P12" t="n">
         <v>408377</v>
@@ -20371,30 +20017,30 @@
         <v>723</v>
       </c>
       <c r="E13" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F13" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G13" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3320</v>
+        <v>3312</v>
       </c>
       <c r="K13" t="s">
-        <v>3321</v>
+        <v>3313</v>
       </c>
       <c r="L13" t="s">
-        <v>3320</v>
+        <v>3312</v>
       </c>
       <c r="M13" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N13" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O13"/>
       <c r="P13" t="n">
@@ -20415,33 +20061,33 @@
         <v>843</v>
       </c>
       <c r="E14" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F14" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G14" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3245</v>
+        <v>3237</v>
       </c>
       <c r="K14" t="s">
-        <v>3322</v>
+        <v>3314</v>
       </c>
       <c r="L14" t="s">
-        <v>3245</v>
+        <v>3237</v>
       </c>
       <c r="M14" t="s">
-        <v>3323</v>
+        <v>3315</v>
       </c>
       <c r="N14" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O14" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
       <c r="P14" t="n">
         <v>410864</v>
@@ -20461,33 +20107,33 @@
         <v>3109</v>
       </c>
       <c r="E15" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F15" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G15" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3324</v>
+        <v>3316</v>
       </c>
       <c r="K15" t="s">
-        <v>3325</v>
+        <v>3317</v>
       </c>
       <c r="L15" t="s">
-        <v>3324</v>
+        <v>3316</v>
       </c>
       <c r="M15" t="s">
-        <v>3326</v>
+        <v>3318</v>
       </c>
       <c r="N15" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O15" t="s">
-        <v>3327</v>
+        <v>3319</v>
       </c>
       <c r="P15" t="n">
         <v>413808</v>
@@ -20507,33 +20153,33 @@
         <v>2265</v>
       </c>
       <c r="E16" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F16" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G16" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3328</v>
+        <v>3320</v>
       </c>
       <c r="K16" t="s">
-        <v>3329</v>
+        <v>3321</v>
       </c>
       <c r="L16" t="s">
-        <v>3328</v>
+        <v>3320</v>
       </c>
       <c r="M16" t="s">
-        <v>3330</v>
+        <v>3322</v>
       </c>
       <c r="N16" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O16" t="s">
-        <v>3331</v>
+        <v>3323</v>
       </c>
       <c r="P16" t="n">
         <v>416895</v>
@@ -20553,33 +20199,33 @@
         <v>1500</v>
       </c>
       <c r="E17" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F17" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G17" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
       <c r="K17" t="s">
-        <v>3332</v>
+        <v>3324</v>
       </c>
       <c r="L17" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
       <c r="M17" t="s">
-        <v>3333</v>
+        <v>3325</v>
       </c>
       <c r="N17" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O17" t="s">
-        <v>3242</v>
+        <v>3234</v>
       </c>
       <c r="P17" t="n">
         <v>419262</v>
@@ -20599,30 +20245,30 @@
         <v>471</v>
       </c>
       <c r="E18" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F18" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G18" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3334</v>
+        <v>3326</v>
       </c>
       <c r="K18" t="s">
-        <v>3335</v>
+        <v>3327</v>
       </c>
       <c r="L18" t="s">
-        <v>3334</v>
+        <v>3326</v>
       </c>
       <c r="M18" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N18" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O18"/>
       <c r="P18" t="n">
@@ -20643,33 +20289,33 @@
         <v>1839</v>
       </c>
       <c r="E19" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F19" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G19" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="K19" t="s">
-        <v>3336</v>
+        <v>3328</v>
       </c>
       <c r="L19" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="M19" t="s">
-        <v>3337</v>
+        <v>3329</v>
       </c>
       <c r="N19" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O19" t="s">
-        <v>3266</v>
+        <v>3258</v>
       </c>
       <c r="P19" t="n">
         <v>421867</v>
@@ -20689,33 +20335,33 @@
         <v>1008</v>
       </c>
       <c r="E20" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F20" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G20" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="K20" t="s">
-        <v>3338</v>
+        <v>3330</v>
       </c>
       <c r="L20" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="M20" t="s">
-        <v>3339</v>
+        <v>3331</v>
       </c>
       <c r="N20" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O20" t="s">
-        <v>3269</v>
+        <v>3261</v>
       </c>
       <c r="P20" t="n">
         <v>423388</v>
@@ -20735,30 +20381,30 @@
         <v>882</v>
       </c>
       <c r="E21" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F21" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G21" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3340</v>
+        <v>3332</v>
       </c>
       <c r="K21" t="s">
-        <v>3341</v>
+        <v>3333</v>
       </c>
       <c r="L21" t="s">
-        <v>3340</v>
+        <v>3332</v>
       </c>
       <c r="M21" t="s">
-        <v>3342</v>
+        <v>3334</v>
       </c>
       <c r="N21" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O21"/>
       <c r="P21" t="n">
@@ -20779,30 +20425,30 @@
         <v>597</v>
       </c>
       <c r="E22" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F22" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G22" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="K22" t="s">
-        <v>3343</v>
+        <v>3335</v>
       </c>
       <c r="L22" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="M22" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N22" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O22"/>
       <c r="P22" t="n">
@@ -20823,33 +20469,33 @@
         <v>1440</v>
       </c>
       <c r="E23" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F23" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G23" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3344</v>
+        <v>3336</v>
       </c>
       <c r="K23" t="s">
-        <v>3345</v>
+        <v>3337</v>
       </c>
       <c r="L23" t="s">
-        <v>3344</v>
+        <v>3336</v>
       </c>
       <c r="M23" t="s">
-        <v>3346</v>
+        <v>3338</v>
       </c>
       <c r="N23" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O23" t="s">
-        <v>3347</v>
+        <v>3339</v>
       </c>
       <c r="P23" t="n">
         <v>426952</v>
@@ -20869,33 +20515,33 @@
         <v>729</v>
       </c>
       <c r="E24" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F24" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G24" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>3348</v>
+        <v>3340</v>
       </c>
       <c r="K24" t="s">
-        <v>3349</v>
+        <v>3341</v>
       </c>
       <c r="L24" t="s">
-        <v>3348</v>
+        <v>3340</v>
       </c>
       <c r="M24" t="s">
-        <v>3350</v>
+        <v>3342</v>
       </c>
       <c r="N24" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O24" t="s">
-        <v>3351</v>
+        <v>3343</v>
       </c>
       <c r="P24" t="n">
         <v>428291</v>
@@ -20915,33 +20561,33 @@
         <v>906</v>
       </c>
       <c r="E25" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F25" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G25" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>3224</v>
+        <v>3216</v>
       </c>
       <c r="K25" t="s">
-        <v>3352</v>
+        <v>3344</v>
       </c>
       <c r="L25" t="s">
-        <v>3224</v>
+        <v>3216</v>
       </c>
       <c r="M25" t="s">
-        <v>3353</v>
+        <v>3345</v>
       </c>
       <c r="N25" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O25" t="s">
-        <v>3225</v>
+        <v>3217</v>
       </c>
       <c r="P25" t="n">
         <v>429164</v>
@@ -20961,33 +20607,33 @@
         <v>1431</v>
       </c>
       <c r="E26" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F26" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G26" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>3354</v>
+        <v>3346</v>
       </c>
       <c r="K26" t="s">
-        <v>3355</v>
+        <v>3347</v>
       </c>
       <c r="L26" t="s">
-        <v>3354</v>
+        <v>3346</v>
       </c>
       <c r="M26" t="s">
-        <v>3356</v>
+        <v>3348</v>
       </c>
       <c r="N26" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O26" t="s">
-        <v>3357</v>
+        <v>3349</v>
       </c>
       <c r="P26" t="n">
         <v>430654</v>
@@ -21007,30 +20653,30 @@
         <v>405</v>
       </c>
       <c r="E27" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F27" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G27" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>3358</v>
+        <v>3350</v>
       </c>
       <c r="K27" t="s">
-        <v>3359</v>
+        <v>3351</v>
       </c>
       <c r="L27" t="s">
-        <v>3358</v>
+        <v>3350</v>
       </c>
       <c r="M27" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N27" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O27"/>
       <c r="P27" t="n">
@@ -21051,33 +20697,33 @@
         <v>1503</v>
       </c>
       <c r="E28" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F28" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G28" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>3360</v>
+        <v>3352</v>
       </c>
       <c r="K28" t="s">
-        <v>3361</v>
+        <v>3353</v>
       </c>
       <c r="L28" t="s">
-        <v>3360</v>
+        <v>3352</v>
       </c>
       <c r="M28" t="s">
-        <v>3362</v>
+        <v>3354</v>
       </c>
       <c r="N28" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O28" t="s">
-        <v>3363</v>
+        <v>3355</v>
       </c>
       <c r="P28" t="n">
         <v>433339</v>
@@ -21097,33 +20743,33 @@
         <v>1242</v>
       </c>
       <c r="E29" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F29" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G29" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>3364</v>
+        <v>3356</v>
       </c>
       <c r="K29" t="s">
-        <v>3365</v>
+        <v>3357</v>
       </c>
       <c r="L29" t="s">
-        <v>3364</v>
+        <v>3356</v>
       </c>
       <c r="M29" t="s">
-        <v>3366</v>
+        <v>3358</v>
       </c>
       <c r="N29" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O29" t="s">
-        <v>3367</v>
+        <v>3359</v>
       </c>
       <c r="P29" t="n">
         <v>435144</v>
@@ -21143,33 +20789,33 @@
         <v>453</v>
       </c>
       <c r="E30" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F30" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G30" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>3368</v>
+        <v>3360</v>
       </c>
       <c r="K30" t="s">
-        <v>3369</v>
+        <v>3361</v>
       </c>
       <c r="L30" t="s">
-        <v>3368</v>
+        <v>3360</v>
       </c>
       <c r="M30" t="s">
-        <v>3370</v>
+        <v>3362</v>
       </c>
       <c r="N30" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O30" t="s">
-        <v>3371</v>
+        <v>3363</v>
       </c>
       <c r="P30" t="n">
         <v>444805</v>
@@ -21189,33 +20835,33 @@
         <v>4536</v>
       </c>
       <c r="E31" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F31" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G31" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>3372</v>
+        <v>3364</v>
       </c>
       <c r="K31" t="s">
-        <v>3373</v>
+        <v>3365</v>
       </c>
       <c r="L31" t="s">
-        <v>3372</v>
+        <v>3364</v>
       </c>
       <c r="M31" t="s">
-        <v>3374</v>
+        <v>3366</v>
       </c>
       <c r="N31" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O31" t="s">
-        <v>3375</v>
+        <v>3367</v>
       </c>
       <c r="P31" t="n">
         <v>448110</v>
@@ -21235,33 +20881,33 @@
         <v>1149</v>
       </c>
       <c r="E32" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F32" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G32" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>3222</v>
+        <v>3214</v>
       </c>
       <c r="K32" t="s">
-        <v>3376</v>
+        <v>3368</v>
       </c>
       <c r="L32" t="s">
-        <v>3222</v>
+        <v>3214</v>
       </c>
       <c r="M32" t="s">
-        <v>3377</v>
+        <v>3369</v>
       </c>
       <c r="N32" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O32" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="P32" t="n">
         <v>452483</v>
@@ -21281,33 +20927,33 @@
         <v>306</v>
       </c>
       <c r="E33" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F33" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G33" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>3378</v>
+        <v>3370</v>
       </c>
       <c r="K33" t="s">
-        <v>3379</v>
+        <v>3371</v>
       </c>
       <c r="L33" t="s">
-        <v>3378</v>
+        <v>3370</v>
       </c>
       <c r="M33" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N33" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O33" t="s">
-        <v>3380</v>
+        <v>3372</v>
       </c>
       <c r="P33" t="n">
         <v>453582</v>
@@ -21327,33 +20973,33 @@
         <v>999</v>
       </c>
       <c r="E34" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F34" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G34" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>3255</v>
+        <v>3247</v>
       </c>
       <c r="K34" t="s">
-        <v>3381</v>
+        <v>3373</v>
       </c>
       <c r="L34" t="s">
-        <v>3255</v>
+        <v>3247</v>
       </c>
       <c r="M34" t="s">
-        <v>3342</v>
+        <v>3334</v>
       </c>
       <c r="N34" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O34" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="P34" t="n">
         <v>454491</v>
@@ -21373,33 +21019,33 @@
         <v>906</v>
       </c>
       <c r="E35" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F35" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G35" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>3382</v>
+        <v>3374</v>
       </c>
       <c r="K35" t="s">
-        <v>3383</v>
+        <v>3375</v>
       </c>
       <c r="L35" t="s">
-        <v>3382</v>
+        <v>3374</v>
       </c>
       <c r="M35" t="s">
-        <v>3384</v>
+        <v>3376</v>
       </c>
       <c r="N35" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O35" t="s">
-        <v>3385</v>
+        <v>3377</v>
       </c>
       <c r="P35" t="n">
         <v>456212</v>
@@ -21419,33 +21065,33 @@
         <v>1341</v>
       </c>
       <c r="E36" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F36" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G36" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>3229</v>
+        <v>3221</v>
       </c>
       <c r="K36" t="s">
-        <v>3386</v>
+        <v>3378</v>
       </c>
       <c r="L36" t="s">
-        <v>3229</v>
+        <v>3221</v>
       </c>
       <c r="M36" t="s">
-        <v>3387</v>
+        <v>3379</v>
       </c>
       <c r="N36" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O36" t="s">
-        <v>3230</v>
+        <v>3222</v>
       </c>
       <c r="P36" t="n">
         <v>457788</v>
@@ -21465,33 +21111,33 @@
         <v>880</v>
       </c>
       <c r="E37" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F37" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G37" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>3388</v>
+        <v>3380</v>
       </c>
       <c r="K37" t="s">
-        <v>3389</v>
+        <v>3381</v>
       </c>
       <c r="L37" t="s">
-        <v>3388</v>
+        <v>3380</v>
       </c>
       <c r="M37" t="s">
-        <v>3390</v>
+        <v>3382</v>
       </c>
       <c r="N37" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O37" t="s">
-        <v>3391</v>
+        <v>3383</v>
       </c>
       <c r="P37" t="n">
         <v>459238</v>
@@ -21511,33 +21157,33 @@
         <v>597</v>
       </c>
       <c r="E38" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F38" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G38" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>3392</v>
+        <v>3384</v>
       </c>
       <c r="K38" t="s">
-        <v>3393</v>
+        <v>3385</v>
       </c>
       <c r="L38" t="s">
-        <v>3392</v>
+        <v>3384</v>
       </c>
       <c r="M38" t="s">
-        <v>3394</v>
+        <v>3386</v>
       </c>
       <c r="N38" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O38" t="s">
-        <v>3395</v>
+        <v>3387</v>
       </c>
       <c r="P38" t="n">
         <v>460261</v>
@@ -21557,33 +21203,33 @@
         <v>1188</v>
       </c>
       <c r="E39" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F39" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G39" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="K39" t="s">
-        <v>3396</v>
+        <v>3388</v>
       </c>
       <c r="L39" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="M39" t="s">
-        <v>3397</v>
+        <v>3389</v>
       </c>
       <c r="N39" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O39" t="s">
-        <v>3260</v>
+        <v>3252</v>
       </c>
       <c r="P39" t="n">
         <v>461372</v>
@@ -21603,33 +21249,33 @@
         <v>1359</v>
       </c>
       <c r="E40" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F40" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G40" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="K40" t="s">
-        <v>3398</v>
+        <v>3390</v>
       </c>
       <c r="L40" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="M40" t="s">
-        <v>3399</v>
+        <v>3391</v>
       </c>
       <c r="N40" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O40" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="P40" t="n">
         <v>463160</v>
@@ -21649,33 +21295,33 @@
         <v>1248</v>
       </c>
       <c r="E41" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F41" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G41" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" t="s">
-        <v>3253</v>
+        <v>3245</v>
       </c>
       <c r="K41" t="s">
-        <v>3400</v>
+        <v>3392</v>
       </c>
       <c r="L41" t="s">
-        <v>3253</v>
+        <v>3245</v>
       </c>
       <c r="M41" t="s">
-        <v>3401</v>
+        <v>3393</v>
       </c>
       <c r="N41" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O41" t="s">
-        <v>3254</v>
+        <v>3246</v>
       </c>
       <c r="P41" t="n">
         <v>465024</v>
@@ -21695,33 +21341,33 @@
         <v>300</v>
       </c>
       <c r="E42" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F42" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G42" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" t="s">
-        <v>3402</v>
+        <v>3394</v>
       </c>
       <c r="K42" t="s">
-        <v>3403</v>
+        <v>3395</v>
       </c>
       <c r="L42" t="s">
-        <v>3402</v>
+        <v>3394</v>
       </c>
       <c r="M42" t="s">
-        <v>3404</v>
+        <v>3396</v>
       </c>
       <c r="N42" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O42" t="s">
-        <v>3405</v>
+        <v>3397</v>
       </c>
       <c r="P42" t="n">
         <v>466112</v>
@@ -21741,33 +21387,33 @@
         <v>300</v>
       </c>
       <c r="E43" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F43" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G43" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" t="s">
-        <v>3406</v>
+        <v>3398</v>
       </c>
       <c r="K43" t="s">
-        <v>3407</v>
+        <v>3399</v>
       </c>
       <c r="L43" t="s">
-        <v>3406</v>
+        <v>3398</v>
       </c>
       <c r="M43" t="s">
-        <v>3408</v>
+        <v>3400</v>
       </c>
       <c r="N43" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O43" t="s">
-        <v>3409</v>
+        <v>3401</v>
       </c>
       <c r="P43" t="n">
         <v>466794</v>
@@ -21787,33 +21433,33 @@
         <v>2397</v>
       </c>
       <c r="E44" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F44" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G44" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44" t="s">
-        <v>3270</v>
+        <v>3262</v>
       </c>
       <c r="K44" t="s">
-        <v>3410</v>
+        <v>3402</v>
       </c>
       <c r="L44" t="s">
-        <v>3270</v>
+        <v>3262</v>
       </c>
       <c r="M44" t="s">
-        <v>3411</v>
+        <v>3403</v>
       </c>
       <c r="N44" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O44" t="s">
-        <v>3272</v>
+        <v>3264</v>
       </c>
       <c r="P44" t="n">
         <v>468458</v>
@@ -21833,33 +21479,33 @@
         <v>2058</v>
       </c>
       <c r="E45" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F45" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G45" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" t="s">
-        <v>3412</v>
+        <v>3404</v>
       </c>
       <c r="K45" t="s">
-        <v>3413</v>
+        <v>3405</v>
       </c>
       <c r="L45" t="s">
-        <v>3412</v>
+        <v>3404</v>
       </c>
       <c r="M45" t="s">
-        <v>3414</v>
+        <v>3406</v>
       </c>
       <c r="N45" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O45" t="s">
-        <v>3415</v>
+        <v>3407</v>
       </c>
       <c r="P45" t="n">
         <v>470968</v>
@@ -21879,33 +21525,33 @@
         <v>1668</v>
       </c>
       <c r="E46" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F46" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G46" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="K46" t="s">
-        <v>3416</v>
+        <v>3408</v>
       </c>
       <c r="L46" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="M46" t="s">
-        <v>3417</v>
+        <v>3409</v>
       </c>
       <c r="N46" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O46" t="s">
-        <v>3249</v>
+        <v>3241</v>
       </c>
       <c r="P46" t="n">
         <v>473874</v>
@@ -21925,33 +21571,33 @@
         <v>624</v>
       </c>
       <c r="E47" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F47" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G47" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47" t="s">
-        <v>3418</v>
+        <v>3410</v>
       </c>
       <c r="K47" t="s">
-        <v>3419</v>
+        <v>3411</v>
       </c>
       <c r="L47" t="s">
-        <v>3418</v>
+        <v>3410</v>
       </c>
       <c r="M47" t="s">
-        <v>3420</v>
+        <v>3412</v>
       </c>
       <c r="N47" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O47" t="s">
-        <v>3421</v>
+        <v>3413</v>
       </c>
       <c r="P47" t="n">
         <v>475430</v>
@@ -21971,33 +21617,33 @@
         <v>3009</v>
       </c>
       <c r="E48" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F48" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G48" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>3422</v>
+        <v>3414</v>
       </c>
       <c r="K48" t="s">
-        <v>3423</v>
+        <v>3415</v>
       </c>
       <c r="L48" t="s">
-        <v>3422</v>
+        <v>3414</v>
       </c>
       <c r="M48" t="s">
-        <v>3424</v>
+        <v>3416</v>
       </c>
       <c r="N48" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O48" t="s">
-        <v>3425</v>
+        <v>3417</v>
       </c>
       <c r="P48" t="n">
         <v>477497</v>
@@ -22017,30 +21663,30 @@
         <v>951</v>
       </c>
       <c r="E49" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F49" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G49" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H49"/>
       <c r="I49"/>
       <c r="J49" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="K49" t="s">
-        <v>3426</v>
+        <v>3418</v>
       </c>
       <c r="L49" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="M49" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N49" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O49"/>
       <c r="P49" t="n">
@@ -22061,30 +21707,30 @@
         <v>192</v>
       </c>
       <c r="E50" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F50" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G50" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H50"/>
       <c r="I50"/>
       <c r="J50" t="s">
-        <v>3427</v>
+        <v>3419</v>
       </c>
       <c r="K50" t="s">
-        <v>3428</v>
+        <v>3420</v>
       </c>
       <c r="L50" t="s">
-        <v>3427</v>
+        <v>3419</v>
       </c>
       <c r="M50" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="N50" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="O50"/>
       <c r="P50" t="n">
@@ -22105,33 +21751,33 @@
         <v>534</v>
       </c>
       <c r="E51" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="F51" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G51" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
       <c r="J51" t="s">
-        <v>3219</v>
+        <v>3211</v>
       </c>
       <c r="K51" t="s">
-        <v>3429</v>
+        <v>3421</v>
       </c>
       <c r="L51" t="s">
-        <v>3219</v>
+        <v>3211</v>
       </c>
       <c r="M51" t="s">
-        <v>3430</v>
+        <v>3422</v>
       </c>
       <c r="N51" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O51" t="s">
-        <v>3221</v>
+        <v>3213</v>
       </c>
       <c r="P51" t="n">
         <v>480802</v>
@@ -22151,33 +21797,33 @@
         <v>474</v>
       </c>
       <c r="E52" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="F52" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="G52" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="H52"/>
       <c r="I52"/>
       <c r="J52" t="s">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="K52" t="s">
-        <v>3431</v>
+        <v>3423</v>
       </c>
       <c r="L52" t="s">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="M52" t="s">
-        <v>3432</v>
+        <v>3424</v>
       </c>
       <c r="N52" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="O52" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="P52" t="n">
         <v>481664</v>
@@ -59500,7 +59146,7 @@
         <v>0.00000000000000000541315551772396</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000000000000000184047287602615</v>
+        <v>0.000000000000000189460443120339</v>
       </c>
       <c r="I2" t="n">
         <v>0.000000000000000170941753191283</v>
@@ -59535,10 +59181,10 @@
         <v>0.000762298087956848</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0129590674952664</v>
+        <v>0.0133402165392448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0120362855993187</v>
+        <v>0.0120362855993186</v>
       </c>
       <c r="J3" t="s">
         <v>1643</v>
